--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,784 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,1,1</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.6862,0.1651,0.0741,0.0793</t>
-  </si>
-  <si>
-    <t>0.0184,0.0059,0.0016,0.9913</t>
-  </si>
-  <si>
-    <t>0.7407,0.0186,0.0219,0.1990</t>
-  </si>
-  <si>
-    <t>0.0774,0.0054,0.0006,0.9752</t>
-  </si>
-  <si>
-    <t>0.9949,0.0016,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9936,0.0036,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9875,0.0096,0.0011,0.0007</t>
-  </si>
-  <si>
-    <t>0.9946,0.0020,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9964,0.0014,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9949,0.0031,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9962,0.0013,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9937,0.0030,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.6107,0.0624,0.3730,0.0154</t>
-  </si>
-  <si>
-    <t>0.3894,0.0313,0.6389,0.0033</t>
-  </si>
-  <si>
-    <t>0.3362,0.0124,0.7392,0.0009</t>
-  </si>
-  <si>
-    <t>0.1697,0.0138,0.8420,0.0086</t>
-  </si>
-  <si>
-    <t>0.6115,0.0241,0.4035,0.0229</t>
-  </si>
-  <si>
-    <t>0.0077,0.9900,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.0768,0.9387,0.0069,0.0005</t>
-  </si>
-  <si>
-    <t>0.5687,0.5478,0.0145,0.0021</t>
-  </si>
-  <si>
-    <t>0.4949,0.6926,0.0039,0.0003</t>
-  </si>
-  <si>
-    <t>0.0046,0.9942,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.5011,0.0094,0.3977,0.0567</t>
-  </si>
-  <si>
-    <t>0.3457,0.0186,0.6895,0.0063</t>
-  </si>
-  <si>
-    <t>0.1569,0.0103,0.8873,0.0060</t>
-  </si>
-  <si>
-    <t>0.4682,0.0026,0.6860,0.0045</t>
-  </si>
-  <si>
-    <t>0.1855,0.0029,0.9026,0.0018</t>
-  </si>
-  <si>
-    <t>0.3183,0.0187,0.7246,0.0090</t>
-  </si>
-  <si>
-    <t>0.0085,0.0012,0.9913,0.0014</t>
-  </si>
-  <si>
-    <t>0.3961,0.6421,0.0245,0.0080</t>
-  </si>
-  <si>
-    <t>0.5825,0.1310,0.3579,0.0137</t>
-  </si>
-  <si>
-    <t>0.0011,0.0278,0.9872,0.0147</t>
-  </si>
-  <si>
-    <t>0.0080,0.9753,0.0353,0.0005</t>
-  </si>
-  <si>
-    <t>0.6514,0.2870,0.1055,0.0218</t>
-  </si>
-  <si>
-    <t>0.4437,0.1091,0.4807,0.0153</t>
-  </si>
-  <si>
-    <t>0.5516,0.5666,0.0182,0.0011</t>
-  </si>
-  <si>
-    <t>0.0455,0.9250,0.1789,0.0028</t>
-  </si>
-  <si>
-    <t>0.0294,0.6790,0.5859,0.0441</t>
-  </si>
-  <si>
-    <t>0.0389,0.0687,0.9239,0.0246</t>
-  </si>
-  <si>
-    <t>0.1207,0.1452,0.7827,0.0176</t>
-  </si>
-  <si>
-    <t>0.0281,0.0141,0.9000,0.0766</t>
-  </si>
-  <si>
-    <t>0.0364,0.0865,0.9249,0.0054</t>
-  </si>
-  <si>
-    <t>0.0270,0.9199,0.1141,0.0013</t>
-  </si>
-  <si>
-    <t>0.0312,0.0786,0.9013,0.0442</t>
-  </si>
-  <si>
-    <t>0.0120,0.8779,0.0299,0.6492</t>
-  </si>
-  <si>
-    <t>0.0016,0.9840,0.0397,0.0194</t>
-  </si>
-  <si>
-    <t>0.0016,0.9732,0.3418,0.0057</t>
-  </si>
-  <si>
-    <t>0.0011,0.9901,0.1405,0.0008</t>
-  </si>
-  <si>
-    <t>0.0022,0.1832,0.9893,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.2762,0.9887,0.0001</t>
-  </si>
-  <si>
-    <t>0.0263,0.0540,0.9427,0.0067</t>
-  </si>
-  <si>
-    <t>0.0446,0.0016,0.9784,0.0002</t>
-  </si>
-  <si>
-    <t>0.0029,0.0059,0.9957,0.0004</t>
-  </si>
-  <si>
-    <t>0.0075,0.1830,0.9585,0.0030</t>
-  </si>
-  <si>
-    <t>0.9533,0.0542,0.0062,0.0020</t>
-  </si>
-  <si>
-    <t>0.9866,0.0098,0.0019,0.0008</t>
-  </si>
-  <si>
-    <t>0.9737,0.0108,0.0022,0.0083</t>
-  </si>
-  <si>
-    <t>0.0062,0.0518,0.9875,0.0029</t>
-  </si>
-  <si>
-    <t>0.9647,0.0269,0.0098,0.0020</t>
-  </si>
-  <si>
-    <t>0.9882,0.0068,0.0026,0.0008</t>
-  </si>
-  <si>
-    <t>0.9602,0.0219,0.0109,0.0045</t>
-  </si>
-  <si>
-    <t>0.0107,0.5186,0.9166,0.0015</t>
-  </si>
-  <si>
-    <t>0.0071,0.0992,0.9742,0.0049</t>
-  </si>
-  <si>
-    <t>0.0327,0.1242,0.8611,0.0436</t>
-  </si>
-  <si>
-    <t>0.0013,0.7926,0.9270,0.0003</t>
-  </si>
-  <si>
-    <t>0.0070,0.0170,0.9900,0.0006</t>
-  </si>
-  <si>
-    <t>0.0619,0.7896,0.1154,0.0003</t>
-  </si>
-  <si>
-    <t>0.0483,0.9565,0.0025,0.0002</t>
-  </si>
-  <si>
-    <t>0.6152,0.0282,0.4860,0.0024</t>
-  </si>
-  <si>
-    <t>0.6477,0.2694,0.1126,0.0047</t>
-  </si>
-  <si>
-    <t>0.0189,0.0881,0.9499,0.0113</t>
-  </si>
-  <si>
-    <t>0.0013,0.6557,0.9628,0.0003</t>
-  </si>
-  <si>
-    <t>0.0033,0.8945,0.6169,0.0002</t>
-  </si>
-  <si>
-    <t>0.0032,0.9798,0.1308,0.0006</t>
-  </si>
-  <si>
-    <t>0.0026,0.9536,0.6221,0.0022</t>
-  </si>
-  <si>
-    <t>0.0135,0.0016,0.3813,0.7337</t>
-  </si>
-  <si>
-    <t>0.0124,0.0015,0.0023,0.9919</t>
-  </si>
-  <si>
-    <t>0.0109,0.0205,0.0015,0.9920</t>
-  </si>
-  <si>
-    <t>0.0125,0.0126,0.0034,0.9913</t>
-  </si>
-  <si>
-    <t>0.0162,0.0303,0.0089,0.9863</t>
-  </si>
-  <si>
-    <t>0.0070,0.0023,0.0044,0.9932</t>
-  </si>
-  <si>
-    <t>0.0021,0.9093,0.7671,0.0003</t>
-  </si>
-  <si>
-    <t>0.0011,0.8782,0.9185,0.0003</t>
-  </si>
-  <si>
-    <t>0.0062,0.5523,0.9030,0.0010</t>
-  </si>
-  <si>
-    <t>0.0190,0.7542,0.5888,0.0019</t>
-  </si>
-  <si>
-    <t>0.0005,0.9414,0.7222,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9043,0.8863,0.0000</t>
-  </si>
-  <si>
-    <t>0.9882,0.0061,0.0015,0.0014</t>
-  </si>
-  <si>
-    <t>0.9801,0.0172,0.0038,0.0005</t>
-  </si>
-  <si>
-    <t>0.9885,0.0116,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9947,0.0027,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9928,0.0023,0.0004,0.0012</t>
-  </si>
-  <si>
-    <t>0.9861,0.0147,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.9811,0.0146,0.0031,0.0010</t>
-  </si>
-  <si>
-    <t>0.9877,0.0103,0.0021,0.0004</t>
-  </si>
-  <si>
-    <t>0.9981,0.0007,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9940,0.0031,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9947,0.0011,0.0003,0.0015</t>
-  </si>
-  <si>
-    <t>0.9930,0.0034,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.9969,0.0007,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9955,0.0025,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9944,0.0011,0.0002,0.0020</t>
-  </si>
-  <si>
-    <t>0.9902,0.0030,0.0012,0.0018</t>
-  </si>
-  <si>
-    <t>0.0061,0.0064,0.9776,0.0240</t>
-  </si>
-  <si>
-    <t>0.0057,0.0101,0.9901,0.0004</t>
-  </si>
-  <si>
-    <t>0.6038,0.0101,0.2976,0.0539</t>
-  </si>
-  <si>
-    <t>0.1358,0.0084,0.9003,0.0012</t>
-  </si>
-  <si>
-    <t>0.2686,0.7823,0.0062,0.0055</t>
-  </si>
-  <si>
-    <t>0.0978,0.9091,0.0142,0.0013</t>
-  </si>
-  <si>
-    <t>0.0593,0.9475,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.4457,0.6901,0.0038,0.0004</t>
-  </si>
-  <si>
-    <t>0.1149,0.8962,0.0050,0.0044</t>
-  </si>
-  <si>
-    <t>0.0520,0.9464,0.0080,0.0004</t>
-  </si>
-  <si>
-    <t>0.5959,0.4621,0.0352,0.0024</t>
-  </si>
-  <si>
-    <t>0.6758,0.0554,0.2995,0.0076</t>
-  </si>
-  <si>
-    <t>0.5038,0.0127,0.5849,0.0098</t>
-  </si>
-  <si>
-    <t>0.2863,0.4906,0.1472,0.2495</t>
-  </si>
-  <si>
-    <t>0.5862,0.0597,0.3551,0.0847</t>
-  </si>
-  <si>
-    <t>0.0388,0.2600,0.0294,0.9450</t>
-  </si>
-  <si>
-    <t>0.0056,0.9862,0.0167,0.0009</t>
-  </si>
-  <si>
-    <t>0.0014,0.9781,0.0101,0.1599</t>
-  </si>
-  <si>
-    <t>0.0117,0.9597,0.0439,0.0231</t>
-  </si>
-  <si>
-    <t>0.0003,0.9571,0.9395,0.0001</t>
-  </si>
-  <si>
-    <t>0.0118,0.9764,0.0696,0.0002</t>
-  </si>
-  <si>
-    <t>0.3493,0.7128,0.0464,0.0031</t>
-  </si>
-  <si>
-    <t>0.8025,0.2364,0.0219,0.0010</t>
-  </si>
-  <si>
-    <t>0.9383,0.0436,0.0182,0.0093</t>
-  </si>
-  <si>
-    <t>0.9709,0.0098,0.0077,0.0064</t>
-  </si>
-  <si>
-    <t>0.9850,0.0045,0.0017,0.0045</t>
-  </si>
-  <si>
-    <t>0.9662,0.0088,0.0173,0.0039</t>
-  </si>
-  <si>
-    <t>0.9905,0.0013,0.0004,0.0036</t>
-  </si>
-  <si>
-    <t>0.9702,0.0137,0.0072,0.0052</t>
-  </si>
-  <si>
-    <t>0.9759,0.0105,0.0077,0.0028</t>
-  </si>
-  <si>
-    <t>0.9817,0.0137,0.0031,0.0011</t>
-  </si>
-  <si>
-    <t>0.0036,0.5816,0.9243,0.0007</t>
-  </si>
-  <si>
-    <t>0.0130,0.3524,0.8898,0.0006</t>
-  </si>
-  <si>
-    <t>0.0121,0.1747,0.9431,0.0021</t>
-  </si>
-  <si>
-    <t>0.0351,0.1735,0.8863,0.0060</t>
-  </si>
-  <si>
-    <t>0.8464,0.0289,0.1093,0.0105</t>
-  </si>
-  <si>
-    <t>0.5613,0.0244,0.4886,0.0106</t>
-  </si>
-  <si>
-    <t>0.4158,0.0216,0.6593,0.0051</t>
-  </si>
-  <si>
-    <t>0.7432,0.0127,0.3136,0.0029</t>
-  </si>
-  <si>
-    <t>0.0833,0.0186,0.0121,0.9513</t>
-  </si>
-  <si>
-    <t>0.0011,0.0004,0.0005,0.9989</t>
-  </si>
-  <si>
-    <t>0.0027,0.0103,0.0001,0.9985</t>
-  </si>
-  <si>
-    <t>0.0496,0.0020,0.0009,0.9838</t>
-  </si>
-  <si>
-    <t>0.0134,0.8637,0.5745,0.0023</t>
-  </si>
-  <si>
-    <t>0.9865,0.0064,0.0028,0.0014</t>
-  </si>
-  <si>
-    <t>0.1428,0.8442,0.0245,0.0032</t>
-  </si>
-  <si>
-    <t>0.9754,0.0032,0.0015,0.0143</t>
-  </si>
-  <si>
-    <t>0.8615,0.1952,0.0117,0.0027</t>
-  </si>
-  <si>
-    <t>0.9491,0.0032,0.0026,0.0344</t>
-  </si>
-  <si>
-    <t>0.2326,0.0036,0.0070,0.8724</t>
-  </si>
-  <si>
-    <t>0.9770,0.0054,0.0031,0.0069</t>
-  </si>
-  <si>
-    <t>0.0047,0.1115,0.9694,0.0203</t>
-  </si>
-  <si>
-    <t>0.9176,0.0028,0.0124,0.0381</t>
-  </si>
-  <si>
-    <t>0.9497,0.0050,0.0236,0.0069</t>
-  </si>
-  <si>
-    <t>0.7951,0.1746,0.0511,0.0146</t>
-  </si>
-  <si>
-    <t>0.8832,0.1101,0.0157,0.0013</t>
-  </si>
-  <si>
-    <t>0.8331,0.1523,0.0359,0.0038</t>
-  </si>
-  <si>
-    <t>0.4403,0.4654,0.1184,0.0229</t>
-  </si>
-  <si>
-    <t>0.8179,0.1600,0.0442,0.0084</t>
-  </si>
-  <si>
-    <t>0.9195,0.0376,0.0300,0.0058</t>
-  </si>
-  <si>
-    <t>0.9763,0.0198,0.0053,0.0012</t>
-  </si>
-  <si>
-    <t>0.9919,0.0024,0.0009,0.0016</t>
-  </si>
-  <si>
-    <t>0.9886,0.0062,0.0016,0.0006</t>
-  </si>
-  <si>
-    <t>0.9904,0.0029,0.0016,0.0011</t>
-  </si>
-  <si>
-    <t>0.9724,0.0069,0.0064,0.0061</t>
-  </si>
-  <si>
-    <t>0.9696,0.0070,0.0028,0.0136</t>
-  </si>
-  <si>
-    <t>0.9814,0.0115,0.0015,0.0031</t>
-  </si>
-  <si>
-    <t>0.9918,0.0041,0.0007,0.0011</t>
-  </si>
-  <si>
-    <t>0.6113,0.4042,0.0014,0.0083</t>
-  </si>
-  <si>
-    <t>0.7052,0.4393,0.0057,0.0004</t>
-  </si>
-  <si>
-    <t>0.7609,0.2547,0.0448,0.0041</t>
-  </si>
-  <si>
-    <t>0.5253,0.3904,0.2469,0.0483</t>
-  </si>
-  <si>
-    <t>0.9898,0.0061,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.8075,0.0818,0.0807,0.0775</t>
-  </si>
-  <si>
-    <t>0.8838,0.1346,0.0151,0.0006</t>
-  </si>
-  <si>
-    <t>0.9770,0.0110,0.0070,0.0025</t>
-  </si>
-  <si>
-    <t>0.0065,0.0228,0.9871,0.0034</t>
-  </si>
-  <si>
-    <t>0.9209,0.0739,0.0156,0.0048</t>
-  </si>
-  <si>
-    <t>0.0044,0.0073,0.9918,0.0013</t>
-  </si>
-  <si>
-    <t>0.0029,0.0282,0.9893,0.0023</t>
-  </si>
-  <si>
-    <t>0.3355,0.0095,0.7605,0.0035</t>
-  </si>
-  <si>
-    <t>0.0036,0.0175,0.9930,0.0005</t>
-  </si>
-  <si>
-    <t>0.0092,0.0044,0.9885,0.0013</t>
-  </si>
-  <si>
-    <t>0.0149,0.0031,0.9842,0.0022</t>
-  </si>
-  <si>
-    <t>0.0341,0.0025,0.9798,0.0002</t>
-  </si>
-  <si>
-    <t>0.3666,0.0231,0.6714,0.0095</t>
-  </si>
-  <si>
-    <t>0.3784,0.0410,0.6225,0.0324</t>
-  </si>
-  <si>
-    <t>0.7024,0.0521,0.2962,0.0125</t>
-  </si>
-  <si>
-    <t>0.3391,0.0885,0.6020,0.0074</t>
-  </si>
-  <si>
-    <t>0.4961,0.1321,0.4576,0.0249</t>
-  </si>
-  <si>
-    <t>0.6055,0.0490,0.3723,0.0041</t>
-  </si>
-  <si>
-    <t>0.6498,0.0441,0.2942,0.0475</t>
-  </si>
-  <si>
-    <t>0.1676,0.0120,0.8644,0.0016</t>
-  </si>
-  <si>
-    <t>0.7898,0.3369,0.0077,0.0004</t>
-  </si>
-  <si>
-    <t>0.7194,0.4059,0.0090,0.0003</t>
-  </si>
-  <si>
-    <t>0.7572,0.3438,0.0113,0.0011</t>
-  </si>
-  <si>
-    <t>0.9701,0.0336,0.0037,0.0003</t>
-  </si>
-  <si>
-    <t>0.9363,0.0755,0.0109,0.0020</t>
-  </si>
-  <si>
-    <t>0.5271,0.1048,0.4323,0.0232</t>
-  </si>
-  <si>
-    <t>0.7048,0.0189,0.2808,0.0251</t>
-  </si>
-  <si>
-    <t>0.6288,0.0059,0.1884,0.0732</t>
-  </si>
-  <si>
-    <t>0.5685,0.0159,0.5084,0.0083</t>
-  </si>
-  <si>
-    <t>0.5272,0.0237,0.5393,0.0082</t>
-  </si>
-  <si>
-    <t>0.1331,0.0628,0.7980,0.0449</t>
-  </si>
-  <si>
-    <t>0.0393,0.0811,0.8922,0.0482</t>
-  </si>
-  <si>
-    <t>0.0401,0.2135,0.8769,0.0096</t>
-  </si>
-  <si>
-    <t>0.2250,0.2485,0.5618,0.0204</t>
-  </si>
-  <si>
-    <t>0.0132,0.0839,0.9498,0.0053</t>
-  </si>
-  <si>
-    <t>0.9946,0.0014,0.0001,0.0012</t>
-  </si>
-  <si>
-    <t>0.9860,0.0139,0.0023,0.0004</t>
-  </si>
-  <si>
-    <t>0.9797,0.0050,0.0013,0.0083</t>
-  </si>
-  <si>
-    <t>0.9675,0.0286,0.0083,0.0010</t>
-  </si>
-  <si>
-    <t>0.9872,0.0072,0.0021,0.0015</t>
-  </si>
-  <si>
-    <t>0.9760,0.0122,0.0060,0.0035</t>
-  </si>
-  <si>
-    <t>0.9894,0.0083,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.9771,0.0126,0.0017,0.0027</t>
-  </si>
-  <si>
-    <t>0.1103,0.1102,0.8032,0.0389</t>
-  </si>
-  <si>
-    <t>0.6954,0.0728,0.3012,0.0150</t>
-  </si>
-  <si>
-    <t>0.9192,0.0554,0.0192,0.0082</t>
-  </si>
-  <si>
-    <t>0.0180,0.0035,0.9869,0.0004</t>
-  </si>
-  <si>
-    <t>0.0035,0.0467,0.9867,0.0017</t>
-  </si>
-  <si>
-    <t>0.0067,0.0106,0.9932,0.0002</t>
-  </si>
-  <si>
-    <t>0.0021,0.0028,0.9921,0.0041</t>
-  </si>
-  <si>
-    <t>0.0416,0.0394,0.9312,0.0076</t>
-  </si>
-  <si>
-    <t>0.0006,0.0060,0.9977,0.0004</t>
-  </si>
-  <si>
-    <t>0.0050,0.0058,0.9921,0.0009</t>
-  </si>
-  <si>
-    <t>0.1196,0.0911,0.8422,0.0048</t>
-  </si>
-  <si>
-    <t>0.8476,0.0030,0.1741,0.0038</t>
-  </si>
-  <si>
-    <t>0.6269,0.0052,0.4806,0.0094</t>
-  </si>
-  <si>
-    <t>0.7998,0.0077,0.2280,0.0063</t>
-  </si>
-  <si>
-    <t>0.9943,0.0035,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9729,0.0333,0.0031,0.0007</t>
-  </si>
-  <si>
-    <t>0.9811,0.0210,0.0039,0.0005</t>
-  </si>
-  <si>
-    <t>0.9837,0.0091,0.0035,0.0013</t>
-  </si>
-  <si>
-    <t>0.9898,0.0053,0.0005,0.0012</t>
-  </si>
-  <si>
-    <t>0.9862,0.0064,0.0023,0.0020</t>
-  </si>
-  <si>
-    <t>0.9846,0.0177,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.9840,0.0092,0.0024,0.0014</t>
-  </si>
-  <si>
-    <t>0.0133,0.0085,0.9858,0.0004</t>
-  </si>
-  <si>
-    <t>0.0051,0.0181,0.9898,0.0006</t>
-  </si>
-  <si>
-    <t>0.0089,0.0093,0.9872,0.0012</t>
-  </si>
-  <si>
-    <t>0.1216,0.0730,0.8217,0.0079</t>
-  </si>
-  <si>
-    <t>0.0012,0.0067,0.9927,0.0059</t>
-  </si>
-  <si>
-    <t>0.2896,0.0080,0.6702,0.0544</t>
-  </si>
-  <si>
-    <t>0.4971,0.0334,0.5455,0.0173</t>
-  </si>
-  <si>
-    <t>0.0160,0.0374,0.9645,0.0109</t>
-  </si>
-  <si>
-    <t>0.6374,0.0049,0.0272,0.3492</t>
-  </si>
-  <si>
-    <t>0.0102,0.1985,0.0048,0.9884</t>
-  </si>
-  <si>
-    <t>0.0124,0.0022,0.0010,0.9938</t>
-  </si>
-  <si>
-    <t>0.0211,0.0006,0.0014,0.9892</t>
-  </si>
-  <si>
-    <t>0.0053,0.0008,0.0002,0.9981</t>
-  </si>
-  <si>
-    <t>0.8620,0.0597,0.0333,0.0459</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.8563,0.0778,0.0298,0.0270</t>
+  </si>
+  <si>
+    <t>0.0285,0.0672,0.0014,0.9823</t>
+  </si>
+  <si>
+    <t>0.8190,0.0069,0.0497,0.0896</t>
+  </si>
+  <si>
+    <t>0.2008,0.0057,0.0045,0.9064</t>
+  </si>
+  <si>
+    <t>0.9928,0.0040,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9918,0.0046,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9881,0.0046,0.0029,0.0012</t>
+  </si>
+  <si>
+    <t>0.9961,0.0020,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9817,0.0114,0.0035,0.0014</t>
+  </si>
+  <si>
+    <t>0.9973,0.0007,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9966,0.0012,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9887,0.0040,0.0015,0.0025</t>
+  </si>
+  <si>
+    <t>0.5982,0.0454,0.4107,0.0309</t>
+  </si>
+  <si>
+    <t>0.2698,0.0702,0.6886,0.0049</t>
+  </si>
+  <si>
+    <t>0.4123,0.0227,0.6761,0.0025</t>
+  </si>
+  <si>
+    <t>0.1688,0.0087,0.8621,0.0035</t>
+  </si>
+  <si>
+    <t>0.5192,0.0365,0.5262,0.0182</t>
+  </si>
+  <si>
+    <t>0.2189,0.8540,0.0105,0.0005</t>
+  </si>
+  <si>
+    <t>0.0281,0.9708,0.0058,0.0003</t>
+  </si>
+  <si>
+    <t>0.1055,0.9006,0.0186,0.0024</t>
+  </si>
+  <si>
+    <t>0.2058,0.8847,0.0029,0.0002</t>
+  </si>
+  <si>
+    <t>0.0066,0.9924,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.4812,0.0391,0.5173,0.0290</t>
+  </si>
+  <si>
+    <t>0.5900,0.0038,0.3455,0.0287</t>
+  </si>
+  <si>
+    <t>0.0772,0.0024,0.9579,0.0015</t>
+  </si>
+  <si>
+    <t>0.3498,0.0057,0.6611,0.0399</t>
+  </si>
+  <si>
+    <t>0.1783,0.0036,0.8772,0.0058</t>
+  </si>
+  <si>
+    <t>0.3083,0.0021,0.7877,0.0046</t>
+  </si>
+  <si>
+    <t>0.0111,0.0064,0.9774,0.0088</t>
+  </si>
+  <si>
+    <t>0.2722,0.7003,0.0773,0.0011</t>
+  </si>
+  <si>
+    <t>0.3726,0.1164,0.5809,0.0063</t>
+  </si>
+  <si>
+    <t>0.0003,0.0065,0.9977,0.0015</t>
+  </si>
+  <si>
+    <t>0.0274,0.6171,0.4965,0.0053</t>
+  </si>
+  <si>
+    <t>0.6090,0.3701,0.0986,0.0241</t>
+  </si>
+  <si>
+    <t>0.8013,0.0228,0.2124,0.0033</t>
+  </si>
+  <si>
+    <t>0.6899,0.3732,0.0242,0.0011</t>
+  </si>
+  <si>
+    <t>0.0600,0.8977,0.1948,0.0025</t>
+  </si>
+  <si>
+    <t>0.0284,0.8706,0.2024,0.0018</t>
+  </si>
+  <si>
+    <t>0.0925,0.0726,0.8604,0.0305</t>
+  </si>
+  <si>
+    <t>0.0520,0.0222,0.9469,0.0029</t>
+  </si>
+  <si>
+    <t>0.0212,0.0028,0.5387,0.5830</t>
+  </si>
+  <si>
+    <t>0.0470,0.1145,0.8793,0.0032</t>
+  </si>
+  <si>
+    <t>0.0022,0.9925,0.0319,0.0000</t>
+  </si>
+  <si>
+    <t>0.0436,0.1230,0.9161,0.0108</t>
+  </si>
+  <si>
+    <t>0.0732,0.5033,0.0338,0.8815</t>
+  </si>
+  <si>
+    <t>0.0025,0.9698,0.0383,0.0994</t>
+  </si>
+  <si>
+    <t>0.0011,0.9849,0.2636,0.0024</t>
+  </si>
+  <si>
+    <t>0.0010,0.9913,0.0770,0.0013</t>
+  </si>
+  <si>
+    <t>0.0191,0.1519,0.9499,0.0076</t>
+  </si>
+  <si>
+    <t>0.0077,0.5793,0.8665,0.0079</t>
+  </si>
+  <si>
+    <t>0.0272,0.0339,0.9467,0.0157</t>
+  </si>
+  <si>
+    <t>0.1972,0.0026,0.8930,0.0035</t>
+  </si>
+  <si>
+    <t>0.0012,0.0057,0.9941,0.0025</t>
+  </si>
+  <si>
+    <t>0.0185,0.1704,0.9287,0.0132</t>
+  </si>
+  <si>
+    <t>0.9761,0.0181,0.0047,0.0011</t>
+  </si>
+  <si>
+    <t>0.9684,0.0288,0.0059,0.0011</t>
+  </si>
+  <si>
+    <t>0.8930,0.0661,0.0569,0.0033</t>
+  </si>
+  <si>
+    <t>0.0047,0.1092,0.9859,0.0025</t>
+  </si>
+  <si>
+    <t>0.9672,0.0135,0.0162,0.0023</t>
+  </si>
+  <si>
+    <t>0.9953,0.0011,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9880,0.0047,0.0021,0.0017</t>
+  </si>
+  <si>
+    <t>0.0077,0.7068,0.8828,0.0020</t>
+  </si>
+  <si>
+    <t>0.0010,0.0179,0.9958,0.0007</t>
+  </si>
+  <si>
+    <t>0.0089,0.0553,0.9729,0.0081</t>
+  </si>
+  <si>
+    <t>0.0020,0.8310,0.9149,0.0010</t>
+  </si>
+  <si>
+    <t>0.0061,0.0091,0.9910,0.0008</t>
+  </si>
+  <si>
+    <t>0.0491,0.9256,0.0525,0.0006</t>
+  </si>
+  <si>
+    <t>0.0196,0.9811,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.2885,0.0786,0.7308,0.0063</t>
+  </si>
+  <si>
+    <t>0.4783,0.3719,0.1738,0.0051</t>
+  </si>
+  <si>
+    <t>0.1148,0.2791,0.6015,0.0211</t>
+  </si>
+  <si>
+    <t>0.0059,0.8726,0.7156,0.0011</t>
+  </si>
+  <si>
+    <t>0.0038,0.8801,0.7661,0.0006</t>
+  </si>
+  <si>
+    <t>0.0017,0.9881,0.0560,0.0007</t>
+  </si>
+  <si>
+    <t>0.0006,0.7769,0.9524,0.0022</t>
+  </si>
+  <si>
+    <t>0.0209,0.0042,0.0106,0.9826</t>
+  </si>
+  <si>
+    <t>0.0034,0.0108,0.0007,0.9977</t>
+  </si>
+  <si>
+    <t>0.0125,0.0008,0.0027,0.9906</t>
+  </si>
+  <si>
+    <t>0.0029,0.0212,0.0009,0.9974</t>
+  </si>
+  <si>
+    <t>0.0093,0.0006,0.0022,0.9928</t>
+  </si>
+  <si>
+    <t>0.0143,0.0020,0.0027,0.9911</t>
+  </si>
+  <si>
+    <t>0.0018,0.7645,0.8867,0.0007</t>
+  </si>
+  <si>
+    <t>0.0050,0.5404,0.9545,0.0015</t>
+  </si>
+  <si>
+    <t>0.0883,0.3627,0.5846,0.0051</t>
+  </si>
+  <si>
+    <t>0.0065,0.4911,0.9166,0.0023</t>
+  </si>
+  <si>
+    <t>0.0008,0.9842,0.3533,0.0002</t>
+  </si>
+  <si>
+    <t>0.0078,0.7877,0.8261,0.0021</t>
+  </si>
+  <si>
+    <t>0.9914,0.0043,0.0008,0.0011</t>
+  </si>
+  <si>
+    <t>0.9633,0.0378,0.0023,0.0025</t>
+  </si>
+  <si>
+    <t>0.9744,0.0325,0.0032,0.0005</t>
+  </si>
+  <si>
+    <t>0.9770,0.0361,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.9783,0.0169,0.0047,0.0008</t>
+  </si>
+  <si>
+    <t>0.9967,0.0017,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9844,0.0121,0.0025,0.0009</t>
+  </si>
+  <si>
+    <t>0.9612,0.0685,0.0027,0.0002</t>
+  </si>
+  <si>
+    <t>0.9967,0.0014,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0008,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9937,0.0023,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9931,0.0024,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9961,0.0015,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9951,0.0029,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9963,0.0007,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9950,0.0027,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.0031,0.9949,0.0032</t>
+  </si>
+  <si>
+    <t>0.1806,0.0032,0.8979,0.0013</t>
+  </si>
+  <si>
+    <t>0.5794,0.0118,0.4016,0.0395</t>
+  </si>
+  <si>
+    <t>0.1397,0.0020,0.9144,0.0041</t>
+  </si>
+  <si>
+    <t>0.2685,0.8219,0.0084,0.0008</t>
+  </si>
+  <si>
+    <t>0.1514,0.8703,0.0131,0.0012</t>
+  </si>
+  <si>
+    <t>0.0670,0.9303,0.0126,0.0020</t>
+  </si>
+  <si>
+    <t>0.3791,0.7181,0.0065,0.0004</t>
+  </si>
+  <si>
+    <t>0.0432,0.9558,0.0093,0.0004</t>
+  </si>
+  <si>
+    <t>0.1351,0.8964,0.0061,0.0003</t>
+  </si>
+  <si>
+    <t>0.7592,0.3019,0.0140,0.0003</t>
+  </si>
+  <si>
+    <t>0.6708,0.1172,0.2437,0.0173</t>
+  </si>
+  <si>
+    <t>0.3451,0.0087,0.7423,0.0101</t>
+  </si>
+  <si>
+    <t>0.7410,0.0671,0.1669,0.0326</t>
+  </si>
+  <si>
+    <t>0.4498,0.0703,0.5604,0.0254</t>
+  </si>
+  <si>
+    <t>0.1967,0.3545,0.0624,0.7735</t>
+  </si>
+  <si>
+    <t>0.0020,0.9897,0.0126,0.0025</t>
+  </si>
+  <si>
+    <t>0.0015,0.9908,0.0284,0.0038</t>
+  </si>
+  <si>
+    <t>0.1529,0.7911,0.0216,0.0747</t>
+  </si>
+  <si>
+    <t>0.0026,0.8947,0.8756,0.0017</t>
+  </si>
+  <si>
+    <t>0.0599,0.9405,0.0517,0.0004</t>
+  </si>
+  <si>
+    <t>0.5050,0.4380,0.0873,0.0040</t>
+  </si>
+  <si>
+    <t>0.4552,0.6165,0.0224,0.0007</t>
+  </si>
+  <si>
+    <t>0.9714,0.0131,0.0081,0.0017</t>
+  </si>
+  <si>
+    <t>0.9835,0.0048,0.0008,0.0067</t>
+  </si>
+  <si>
+    <t>0.9787,0.0092,0.0034,0.0037</t>
+  </si>
+  <si>
+    <t>0.9697,0.0211,0.0057,0.0018</t>
+  </si>
+  <si>
+    <t>0.9802,0.0087,0.0050,0.0025</t>
+  </si>
+  <si>
+    <t>0.9084,0.0536,0.0343,0.0225</t>
+  </si>
+  <si>
+    <t>0.9844,0.0084,0.0019,0.0026</t>
+  </si>
+  <si>
+    <t>0.9888,0.0049,0.0026,0.0009</t>
+  </si>
+  <si>
+    <t>0.0033,0.7533,0.9129,0.0007</t>
+  </si>
+  <si>
+    <t>0.0028,0.4824,0.9457,0.0002</t>
+  </si>
+  <si>
+    <t>0.0107,0.5277,0.8743,0.0021</t>
+  </si>
+  <si>
+    <t>0.0866,0.0415,0.8930,0.0023</t>
+  </si>
+  <si>
+    <t>0.6493,0.0267,0.3495,0.0348</t>
+  </si>
+  <si>
+    <t>0.7401,0.0356,0.2381,0.0084</t>
+  </si>
+  <si>
+    <t>0.6555,0.0319,0.3606,0.0222</t>
+  </si>
+  <si>
+    <t>0.4111,0.0467,0.5867,0.0182</t>
+  </si>
+  <si>
+    <t>0.1335,0.0048,0.0043,0.9389</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.0013,0.9978</t>
+  </si>
+  <si>
+    <t>0.0035,0.0115,0.0018,0.9964</t>
+  </si>
+  <si>
+    <t>0.0324,0.0038,0.0028,0.9850</t>
+  </si>
+  <si>
+    <t>0.0100,0.8442,0.6856,0.0035</t>
+  </si>
+  <si>
+    <t>0.9587,0.0521,0.0050,0.0002</t>
+  </si>
+  <si>
+    <t>0.1805,0.8477,0.0028,0.0019</t>
+  </si>
+  <si>
+    <t>0.9932,0.0017,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9157,0.0955,0.0141,0.0008</t>
+  </si>
+  <si>
+    <t>0.9754,0.0021,0.0010,0.0182</t>
+  </si>
+  <si>
+    <t>0.8300,0.0206,0.0907,0.0475</t>
+  </si>
+  <si>
+    <t>0.9899,0.0026,0.0019,0.0017</t>
+  </si>
+  <si>
+    <t>0.0024,0.1117,0.9819,0.0116</t>
+  </si>
+  <si>
+    <t>0.7777,0.0008,0.0027,0.2508</t>
+  </si>
+  <si>
+    <t>0.9545,0.0028,0.0091,0.0134</t>
+  </si>
+  <si>
+    <t>0.3714,0.6152,0.0761,0.0656</t>
+  </si>
+  <si>
+    <t>0.8843,0.0602,0.0329,0.0038</t>
+  </si>
+  <si>
+    <t>0.8324,0.1156,0.0584,0.0007</t>
+  </si>
+  <si>
+    <t>0.7114,0.1113,0.1806,0.0425</t>
+  </si>
+  <si>
+    <t>0.7089,0.2832,0.0366,0.0012</t>
+  </si>
+  <si>
+    <t>0.7772,0.1022,0.1371,0.0055</t>
+  </si>
+  <si>
+    <t>0.9788,0.0113,0.0039,0.0024</t>
+  </si>
+  <si>
+    <t>0.9881,0.0060,0.0018,0.0016</t>
+  </si>
+  <si>
+    <t>0.9807,0.0061,0.0055,0.0027</t>
+  </si>
+  <si>
+    <t>0.9950,0.0008,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.9835,0.0078,0.0043,0.0012</t>
+  </si>
+  <si>
+    <t>0.9801,0.0088,0.0021,0.0043</t>
+  </si>
+  <si>
+    <t>0.9810,0.0097,0.0021,0.0028</t>
+  </si>
+  <si>
+    <t>0.9723,0.0140,0.0077,0.0022</t>
+  </si>
+  <si>
+    <t>0.6346,0.5187,0.0062,0.0007</t>
+  </si>
+  <si>
+    <t>0.3955,0.7174,0.0147,0.0008</t>
+  </si>
+  <si>
+    <t>0.5714,0.5688,0.0090,0.0013</t>
+  </si>
+  <si>
+    <t>0.1313,0.1026,0.8533,0.0039</t>
+  </si>
+  <si>
+    <t>0.9107,0.0756,0.0249,0.0073</t>
+  </si>
+  <si>
+    <t>0.9035,0.0737,0.0314,0.0098</t>
+  </si>
+  <si>
+    <t>0.9821,0.0139,0.0019,0.0010</t>
+  </si>
+  <si>
+    <t>0.9442,0.0525,0.0125,0.0006</t>
+  </si>
+  <si>
+    <t>0.0030,0.0459,0.9914,0.0013</t>
+  </si>
+  <si>
+    <t>0.9248,0.0601,0.0273,0.0030</t>
+  </si>
+  <si>
+    <t>0.0170,0.0028,0.9878,0.0006</t>
+  </si>
+  <si>
+    <t>0.0012,0.1397,0.9923,0.0002</t>
+  </si>
+  <si>
+    <t>0.0452,0.0032,0.9743,0.0004</t>
+  </si>
+  <si>
+    <t>0.0119,0.0468,0.9758,0.0020</t>
+  </si>
+  <si>
+    <t>0.0433,0.0140,0.9606,0.0021</t>
+  </si>
+  <si>
+    <t>0.0129,0.0014,0.9912,0.0004</t>
+  </si>
+  <si>
+    <t>0.0106,0.0073,0.9890,0.0003</t>
+  </si>
+  <si>
+    <t>0.4445,0.0261,0.6202,0.0051</t>
+  </si>
+  <si>
+    <t>0.1034,0.0022,0.9461,0.0009</t>
+  </si>
+  <si>
+    <t>0.2140,0.4094,0.4115,0.0074</t>
+  </si>
+  <si>
+    <t>0.4981,0.1618,0.3625,0.0104</t>
+  </si>
+  <si>
+    <t>0.2929,0.2318,0.5415,0.0094</t>
+  </si>
+  <si>
+    <t>0.6525,0.0906,0.2853,0.0096</t>
+  </si>
+  <si>
+    <t>0.6236,0.0243,0.4063,0.0081</t>
+  </si>
+  <si>
+    <t>0.6349,0.0985,0.3048,0.0091</t>
+  </si>
+  <si>
+    <t>0.8210,0.3180,0.0029,0.0005</t>
+  </si>
+  <si>
+    <t>0.7329,0.3756,0.0145,0.0026</t>
+  </si>
+  <si>
+    <t>0.3957,0.7078,0.0106,0.0015</t>
+  </si>
+  <si>
+    <t>0.9631,0.0492,0.0035,0.0004</t>
+  </si>
+  <si>
+    <t>0.9313,0.0751,0.0102,0.0004</t>
+  </si>
+  <si>
+    <t>0.5838,0.1706,0.2656,0.0572</t>
+  </si>
+  <si>
+    <t>0.7067,0.0368,0.2481,0.0334</t>
+  </si>
+  <si>
+    <t>0.8116,0.0124,0.1029,0.0363</t>
+  </si>
+  <si>
+    <t>0.0626,0.0023,0.9565,0.0034</t>
+  </si>
+  <si>
+    <t>0.6861,0.0079,0.2463,0.0330</t>
+  </si>
+  <si>
+    <t>0.0106,0.0547,0.9160,0.0855</t>
+  </si>
+  <si>
+    <t>0.0290,0.3814,0.8382,0.0030</t>
+  </si>
+  <si>
+    <t>0.0101,0.2230,0.9227,0.0204</t>
+  </si>
+  <si>
+    <t>0.1444,0.0868,0.7966,0.0101</t>
+  </si>
+  <si>
+    <t>0.0024,0.7061,0.8845,0.0005</t>
+  </si>
+  <si>
+    <t>0.9910,0.0049,0.0008,0.0014</t>
+  </si>
+  <si>
+    <t>0.9947,0.0021,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9855,0.0098,0.0011,0.0017</t>
+  </si>
+  <si>
+    <t>0.9910,0.0092,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9855,0.0141,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9842,0.0075,0.0038,0.0020</t>
+  </si>
+  <si>
+    <t>0.9880,0.0069,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.9900,0.0038,0.0017,0.0013</t>
+  </si>
+  <si>
+    <t>0.0656,0.0175,0.9340,0.0064</t>
+  </si>
+  <si>
+    <t>0.2508,0.2520,0.4734,0.0026</t>
+  </si>
+  <si>
+    <t>0.7755,0.1301,0.0160,0.0833</t>
+  </si>
+  <si>
+    <t>0.0095,0.0167,0.9823,0.0010</t>
+  </si>
+  <si>
+    <t>0.0012,0.0188,0.9943,0.0016</t>
+  </si>
+  <si>
+    <t>0.0632,0.0118,0.9517,0.0004</t>
+  </si>
+  <si>
+    <t>0.0048,0.0014,0.9926,0.0019</t>
+  </si>
+  <si>
+    <t>0.0180,0.0225,0.9716,0.0031</t>
+  </si>
+  <si>
+    <t>0.0002,0.0018,0.9990,0.0002</t>
+  </si>
+  <si>
+    <t>0.0276,0.0110,0.9695,0.0024</t>
+  </si>
+  <si>
+    <t>0.2728,0.1048,0.6489,0.0182</t>
+  </si>
+  <si>
+    <t>0.6053,0.0132,0.4382,0.0128</t>
+  </si>
+  <si>
+    <t>0.6920,0.0293,0.2773,0.0229</t>
+  </si>
+  <si>
+    <t>0.7599,0.0409,0.2049,0.0058</t>
+  </si>
+  <si>
+    <t>0.9930,0.0064,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9945,0.0030,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9949,0.0039,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9860,0.0108,0.0034,0.0006</t>
+  </si>
+  <si>
+    <t>0.9849,0.0097,0.0036,0.0008</t>
+  </si>
+  <si>
+    <t>0.9916,0.0050,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.9961,0.0036,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9777,0.0160,0.0035,0.0015</t>
+  </si>
+  <si>
+    <t>0.0426,0.1416,0.8163,0.0054</t>
+  </si>
+  <si>
+    <t>0.0013,0.0099,0.9969,0.0002</t>
+  </si>
+  <si>
+    <t>0.0040,0.0058,0.9934,0.0005</t>
+  </si>
+  <si>
+    <t>0.0412,0.0140,0.9551,0.0021</t>
+  </si>
+  <si>
+    <t>0.0111,0.0024,0.9858,0.0023</t>
+  </si>
+  <si>
+    <t>0.4006,0.0129,0.4124,0.1384</t>
+  </si>
+  <si>
+    <t>0.2528,0.0316,0.7535,0.0216</t>
+  </si>
+  <si>
+    <t>0.0258,0.0308,0.9522,0.0142</t>
+  </si>
+  <si>
+    <t>0.8143,0.0014,0.0096,0.1407</t>
+  </si>
+  <si>
+    <t>0.0030,0.1997,0.0011,0.9957</t>
+  </si>
+  <si>
+    <t>0.0542,0.0208,0.0073,0.9713</t>
+  </si>
+  <si>
+    <t>0.0070,0.0005,0.0003,0.9969</t>
+  </si>
+  <si>
+    <t>0.0087,0.0001,0.0007,0.9953</t>
+  </si>
+  <si>
+    <t>0.7534,0.0195,0.1288,0.0894</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1985,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1999,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2013,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2069,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2083,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2097,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2125,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2139,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2153,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2167,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2181,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,10 +2192,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2209,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2223,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2237,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2251,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2265,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2276,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2290,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2307,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2321,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2335,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2349,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2363,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2377,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2388,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2419,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2433,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2447,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2458,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2486,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2503,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2517,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,10 +2528,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2545,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2559,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2584,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2601,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2615,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2629,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2643,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,10 +2654,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2671,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2699,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2713,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2741,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2755,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2783,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2797,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2811,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2825,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2839,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2853,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2867,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2881,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2895,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,10 +2920,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2934,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2951,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2965,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2979,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2993,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3007,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3021,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3035,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3049,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3063,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3077,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3091,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3105,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3119,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3130,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3144,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,10 +3158,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3175,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3329,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3343,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3371,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3385,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3399,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3413,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3427,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3441,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3455,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3483,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3497,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3511,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3525,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3539,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3553,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3567,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3581,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3595,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3606,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3623,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3637,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3651,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3665,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3679,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3693,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,10 +3704,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3718,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3763,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3777,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3791,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3805,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3833,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3847,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3861,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,10 +3872,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3889,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3903,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3917,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3928,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3942,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3959,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3973,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3987,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +4001,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4015,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4043,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4071,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4085,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4096,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4127,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4141,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4155,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4166,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4211,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4309,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4323,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4362,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4376,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4390,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4404,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4421,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4435,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4449,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4463,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4491,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4547,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4561,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4575,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4589,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4603,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4617,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4628,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4642,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4656,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4673,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4687,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4698,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4715,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4729,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,10 +4740,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4757,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4771,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4785,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4799,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4813,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4827,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4838,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4855,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4869,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4883,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4897,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,10 +4908,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4953,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4967,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4981,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4995,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5009,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5023,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5048,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5065,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5093,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5107,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5121,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5135,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5149,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5163,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5177,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5191,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5205,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5261,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5275,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5289,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5303,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5317,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5331,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5359,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5373,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5387,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5401,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5412,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5429,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5443,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5457,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5471,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5485,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5499,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5513,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5527,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
